--- a/output/Data and Chart Outputs/canada_cer_gas.xlsx
+++ b/output/Data and Chart Outputs/canada_cer_gas.xlsx
@@ -3210,7 +3210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3259,6 +3259,26 @@
           <t>Imports - West (mcm/d)</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Imports (See Disclaimer) - East (mcm/d)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Imports (See Disclaimer) - MidWest (mcm/d)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Imports (See Disclaimer) - Total (mcm/d)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Imports (See Disclaimer) - West (mcm/d)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6263,6 +6283,18 @@
       <c r="I98" t="n">
         <v>0.282</v>
       </c>
+      <c r="J98" t="n">
+        <v>24.639</v>
+      </c>
+      <c r="K98" t="n">
+        <v>64.17400000000001</v>
+      </c>
+      <c r="L98" t="n">
+        <v>178.725</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.282</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6294,6 +6326,18 @@
       <c r="I99" t="n">
         <v>0.658</v>
       </c>
+      <c r="J99" t="n">
+        <v>25.193</v>
+      </c>
+      <c r="K99" t="n">
+        <v>63.546</v>
+      </c>
+      <c r="L99" t="n">
+        <v>179.598</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.658</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6325,6 +6369,18 @@
       <c r="I100" t="n">
         <v>0.273</v>
       </c>
+      <c r="J100" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="K100" t="n">
+        <v>64.163</v>
+      </c>
+      <c r="L100" t="n">
+        <v>180.673</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.273</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6356,6 +6412,18 @@
       <c r="I101" t="n">
         <v>0.664</v>
       </c>
+      <c r="J101" t="n">
+        <v>25.431</v>
+      </c>
+      <c r="K101" t="n">
+        <v>41.797</v>
+      </c>
+      <c r="L101" t="n">
+        <v>135.824</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.664</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6387,6 +6455,18 @@
       <c r="I102" t="n">
         <v>0.04</v>
       </c>
+      <c r="J102" t="n">
+        <v>23.608</v>
+      </c>
+      <c r="K102" t="n">
+        <v>40.454</v>
+      </c>
+      <c r="L102" t="n">
+        <v>128.389</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6415,6 +6495,15 @@
       <c r="H103" t="n">
         <v>122.4</v>
       </c>
+      <c r="J103" t="n">
+        <v>25.559</v>
+      </c>
+      <c r="K103" t="n">
+        <v>35.641</v>
+      </c>
+      <c r="L103" t="n">
+        <v>122.4</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6446,6 +6535,18 @@
       <c r="I104" t="n">
         <v>0.226</v>
       </c>
+      <c r="J104" t="n">
+        <v>24.946</v>
+      </c>
+      <c r="K104" t="n">
+        <v>35.253</v>
+      </c>
+      <c r="L104" t="n">
+        <v>120.85</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.226</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6477,6 +6578,18 @@
       <c r="I105" t="n">
         <v>1.265</v>
       </c>
+      <c r="J105" t="n">
+        <v>26.077</v>
+      </c>
+      <c r="K105" t="n">
+        <v>25.691</v>
+      </c>
+      <c r="L105" t="n">
+        <v>106.065</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.265</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6508,6 +6621,18 @@
       <c r="I106" t="n">
         <v>0.01</v>
       </c>
+      <c r="J106" t="n">
+        <v>25.428</v>
+      </c>
+      <c r="K106" t="n">
+        <v>32.524</v>
+      </c>
+      <c r="L106" t="n">
+        <v>115.925</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6539,6 +6664,18 @@
       <c r="I107" t="n">
         <v>0.449</v>
       </c>
+      <c r="J107" t="n">
+        <v>25.206</v>
+      </c>
+      <c r="K107" t="n">
+        <v>29.175</v>
+      </c>
+      <c r="L107" t="n">
+        <v>109.66</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.449</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6570,6 +6707,18 @@
       <c r="I108" t="n">
         <v>0.181</v>
       </c>
+      <c r="J108" t="n">
+        <v>21.337</v>
+      </c>
+      <c r="K108" t="n">
+        <v>48.007</v>
+      </c>
+      <c r="L108" t="n">
+        <v>139.05</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.181</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6601,6 +6750,18 @@
       <c r="I109" t="n">
         <v>0.12</v>
       </c>
+      <c r="J109" t="n">
+        <v>19.654</v>
+      </c>
+      <c r="K109" t="n">
+        <v>59.271</v>
+      </c>
+      <c r="L109" t="n">
+        <v>158.089</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6632,6 +6793,18 @@
       <c r="I110" t="n">
         <v>1.726</v>
       </c>
+      <c r="J110" t="n">
+        <v>18.184</v>
+      </c>
+      <c r="K110" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="L110" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.726</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6663,6 +6836,18 @@
       <c r="I111" t="n">
         <v>0.03</v>
       </c>
+      <c r="J111" t="n">
+        <v>19.604</v>
+      </c>
+      <c r="K111" t="n">
+        <v>37.686</v>
+      </c>
+      <c r="L111" t="n">
+        <v>114.64</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6694,6 +6879,18 @@
       <c r="I112" t="n">
         <v>0.288</v>
       </c>
+      <c r="J112" t="n">
+        <v>19.006</v>
+      </c>
+      <c r="K112" t="n">
+        <v>36.616</v>
+      </c>
+      <c r="L112" t="n">
+        <v>111.82</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.288</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6725,6 +6922,18 @@
       <c r="I113" t="n">
         <v>0.118</v>
       </c>
+      <c r="J113" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="K113" t="n">
+        <v>16.278</v>
+      </c>
+      <c r="L113" t="n">
+        <v>70.133</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.118</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6756,6 +6965,18 @@
       <c r="I114" t="n">
         <v>0.027</v>
       </c>
+      <c r="J114" t="n">
+        <v>18.015</v>
+      </c>
+      <c r="K114" t="n">
+        <v>14.455</v>
+      </c>
+      <c r="L114" t="n">
+        <v>64.995</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.027</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6787,6 +7008,18 @@
       <c r="I115" t="n">
         <v>0.021</v>
       </c>
+      <c r="J115" t="n">
+        <v>13.269</v>
+      </c>
+      <c r="K115" t="n">
+        <v>15.091</v>
+      </c>
+      <c r="L115" t="n">
+        <v>56.762</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.021</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6818,6 +7051,18 @@
       <c r="I116" t="n">
         <v>0.006</v>
       </c>
+      <c r="J116" t="n">
+        <v>19.413</v>
+      </c>
+      <c r="K116" t="n">
+        <v>14.978</v>
+      </c>
+      <c r="L116" t="n">
+        <v>68.792</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.006</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6847,6 +7092,18 @@
         <v>59.765</v>
       </c>
       <c r="I117" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="J117" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="K117" t="n">
+        <v>15.315</v>
+      </c>
+      <c r="L117" t="n">
+        <v>59.765</v>
+      </c>
+      <c r="M117" t="n">
         <v>0.017</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/canada_cer_gas.xlsx
+++ b/output/Data and Chart Outputs/canada_cer_gas.xlsx
@@ -154,7 +154,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Canada natural gas exports to the US by region (CER) (to Jul/26)</a:t>
+              <a:t>Canada natural gas exports to the US by region (CER) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -184,12 +184,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$92</f>
+              <f>'Chart'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$92</f>
+              <f>'Chart'!$B$2:$B$93</f>
             </numRef>
           </val>
         </ser>
@@ -212,12 +212,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$92</f>
+              <f>'Chart'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$92</f>
+              <f>'Chart'!$C$2:$C$93</f>
             </numRef>
           </val>
         </ser>
@@ -240,12 +240,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$92</f>
+              <f>'Chart'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$92</f>
+              <f>'Chart'!$D$2:$D$93</f>
             </numRef>
           </val>
         </ser>
@@ -346,7 +346,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Canada natural gas exports and imports (CER) (to Jul/26)</a:t>
+              <a:t>Canada natural gas exports and imports (CER) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -382,12 +382,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Exports and imports'!$A$2:$A$92</f>
+              <f>'Chart - Exports and imports'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Exports and imports'!$B$2:$B$92</f>
+              <f>'Chart - Exports and imports'!$B$2:$B$93</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -418,12 +418,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Exports and imports'!$A$2:$A$92</f>
+              <f>'Chart - Exports and imports'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Exports and imports'!$C$2:$C$92</f>
+              <f>'Chart - Exports and imports'!$C$2:$C$93</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -891,7 +891,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Canada, monthly, 2015-01 to 2026-07. Source file: https://www.cer-rec.gc.ca/open/imports-exports/natural-gas-exports-monthly.csv (Last-Modified Sat, 12 Sep 2026 10:05:33 GMT).</t>
+          <t>Canada, monthly, 2015-01 to 2026-08. Source file: https://www.cer-rec.gc.ca/open/imports-exports/natural-gas-exports-monthly.csv (Last-Modified Mon, 12 Oct 2026 10:04:48 GMT).</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lm[imports-exports/natural-gas-exports-monthly.csv]=Sat, 12 Sep 2026 10:05:33 GMT</t>
+          <t>lm[imports-exports/natural-gas-exports-monthly.csv]=Mon, 12 Oct 2026 10:04:48 GMT</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2229,6 +2229,20 @@
       </c>
       <c r="D92" t="n">
         <v>88.006</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B93" t="n">
+        <v>28.983</v>
+      </c>
+      <c r="C93" t="n">
+        <v>109.264</v>
+      </c>
+      <c r="D93" t="n">
+        <v>82.224</v>
       </c>
     </row>
   </sheetData>
@@ -2243,7 +2257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2557,7 +2571,7 @@
         <v>44256</v>
       </c>
       <c r="B28" t="n">
-        <v>432.825</v>
+        <v>432.826</v>
       </c>
       <c r="C28" t="n">
         <v>146.958</v>
@@ -2733,7 +2747,7 @@
         <v>44743</v>
       </c>
       <c r="B44" t="n">
-        <v>457.596</v>
+        <v>457.597</v>
       </c>
       <c r="C44" t="n">
         <v>117.424</v>
@@ -3051,7 +3065,7 @@
         <v>45658</v>
       </c>
       <c r="B74" t="n">
-        <v>604.374</v>
+        <v>604.375</v>
       </c>
     </row>
     <row r="75">
@@ -3196,6 +3210,14 @@
       </c>
       <c r="B92" t="n">
         <v>449.591</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B93" t="n">
+        <v>440.943</v>
       </c>
     </row>
   </sheetData>
@@ -3210,7 +3232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5564,7 +5586,7 @@
         <v>88.98699999999999</v>
       </c>
       <c r="D76" t="n">
-        <v>432.825</v>
+        <v>432.826</v>
       </c>
       <c r="E76" t="n">
         <v>99.18600000000001</v>
@@ -6060,7 +6082,7 @@
         <v>107.351</v>
       </c>
       <c r="D92" t="n">
-        <v>457.596</v>
+        <v>457.597</v>
       </c>
       <c r="E92" t="n">
         <v>94.051</v>
@@ -6939,7 +6961,7 @@
         <v>130.257</v>
       </c>
       <c r="D122" t="n">
-        <v>604.374</v>
+        <v>604.375</v>
       </c>
       <c r="E122" t="n">
         <v>115.838</v>
@@ -7285,6 +7307,25 @@
       </c>
       <c r="E140" t="n">
         <v>88.006</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>28.983</v>
+      </c>
+      <c r="C141" t="n">
+        <v>109.264</v>
+      </c>
+      <c r="D141" t="n">
+        <v>440.943</v>
+      </c>
+      <c r="E141" t="n">
+        <v>82.224</v>
       </c>
     </row>
   </sheetData>
